--- a/footprints/parts_registry.xlsx
+++ b/footprints/parts_registry.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Legend" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'V2000'!$A$5:$M$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'V2000'!$A$5:$M$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -559,7 +559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:P8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -896,30 +896,86 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="n"/>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="n"/>
-      <c r="H5" s="4" t="n"/>
-      <c r="I5" s="4" t="n"/>
-      <c r="J5" s="4" t="n"/>
-      <c r="K5" s="4" t="n"/>
-      <c r="L5" s="4" t="n"/>
-      <c r="M5" s="4" t="n"/>
-      <c r="N5" s="4" t="n"/>
-      <c r="O5" s="4" t="n"/>
-      <c r="P5" s="4" t="n"/>
+    <row r="5" ht="46" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>INDM8084X550-8M</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Eaton EE5.0 SMT (8핀)</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>소형 1.20 x 1.89 / 탭 3.15 x 3.00</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>8.00 x 8.38 x 5.50max</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>x ±4.60 / y ±4.79</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>벤더랜드(소형 1.2x1.6, 탭 2.7x3.0)만큼만 오프셋</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>규칙2로 토 0.50 연장(소형 1.6→1.89, 탭 2.7→3.15). 규칙4 이탈 — 페이스트는 벤더량 유지. TOP/BOTTOM VIEW 미확정</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>미검증</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>buildindm8084.il</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>Eaton ELX1187 p.2 Mechanical / Recommended PCB Layout</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>※ DRC / 검증상태는 axlDRCUpdate(t) 와 extracta 대조를 실제로 돌린 뒤에만 갱신할 것.</t>
-        </is>
-      </c>
+      <c r="A6" s="4" t="n"/>
       <c r="B6" s="4" t="n"/>
       <c r="C6" s="4" t="n"/>
       <c r="D6" s="4" t="n"/>
@@ -939,7 +995,7 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>※ 두 풋프린트 모두 이 세션에서는 빌드하지 못했습니다 (Allegro/extracta 부재). 스크립트만 작성된 상태입니다.</t>
+          <t>※ DRC / 검증상태는 axlDRCUpdate(t) 와 extracta 대조를 실제로 돌린 뒤에만 갱신할 것.</t>
         </is>
       </c>
       <c r="B7" s="4" t="n"/>
@@ -958,6 +1014,28 @@
       <c r="O7" s="4" t="n"/>
       <c r="P7" s="4" t="n"/>
     </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>※ 네 풋프린트 모두 이 세션에서는 빌드하지 못했습니다 (Allegro/extracta 부재). 스크립트만 작성된 상태입니다.</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="4" t="n"/>
+      <c r="E8" s="4" t="n"/>
+      <c r="F8" s="4" t="n"/>
+      <c r="G8" s="4" t="n"/>
+      <c r="H8" s="4" t="n"/>
+      <c r="I8" s="4" t="n"/>
+      <c r="J8" s="4" t="n"/>
+      <c r="K8" s="4" t="n"/>
+      <c r="L8" s="4" t="n"/>
+      <c r="M8" s="4" t="n"/>
+      <c r="N8" s="4" t="n"/>
+      <c r="O8" s="4" t="n"/>
+      <c r="P8" s="4" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -970,7 +1048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1343,66 +1421,131 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="n"/>
-      <c r="B9" s="4" t="n"/>
-      <c r="C9" s="4" t="n"/>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="4" t="n"/>
-      <c r="F9" s="4" t="n"/>
-      <c r="G9" s="4" t="n"/>
-      <c r="H9" s="4" t="n"/>
-      <c r="I9" s="4" t="n"/>
-      <c r="J9" s="4" t="n"/>
-      <c r="K9" s="4" t="n"/>
-      <c r="L9" s="4" t="n"/>
-      <c r="M9" s="4" t="n"/>
+    <row r="9" ht="42" customHeight="1">
+      <c r="A9" s="10">
+        <f>ROW()-5</f>
+        <v/>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>ECST1V0805-1100-R</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>SMT 전류센스 트랜스포머</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>100:1 / Lsec 2000µH min @100kHz / DCR sec 5.5Ω max / pri 0.7mΩ / Hi-pot 500Vac / 10A / 50kHz~1MHz / -40~+125°C</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>EE5.0 SMT 8핀</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>INDM8084X550-8M</t>
+        </is>
+      </c>
+      <c r="H9" s="11">
+        <f>IFERROR(INDEX(Footprints!$D$2:$D$1000,MATCH($G9,Footprints!$A$2:$A$1000,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Eaton ELX1187 (2022-04)</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>buildindm8084.il</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>미검증</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>Pri=8(dot)-7(대형탭), Sec=1(dot)-3, 2/4/5/6=NC. 평면도 TOP/BOTTOM 미확정 — 뒤집히면 1↔3, 7↔8 극성 반전. 부품 아래 배선·비아 금지(데이터시트)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n"/>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>예시)  GRM188R71C104KA01D</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>Murata</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>MLCC</t>
-        </is>
-      </c>
-      <c r="E10" s="12" t="inlineStr">
-        <is>
-          <t>100nF ±10% / 16V / X7R</t>
-        </is>
-      </c>
-      <c r="F10" s="12" t="inlineStr">
-        <is>
-          <t>0603</t>
-        </is>
-      </c>
-      <c r="G10" s="12" t="inlineStr">
-        <is>
-          <t>CAPC1608X90N</t>
-        </is>
-      </c>
+      <c r="B10" s="4" t="n"/>
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="4" t="n"/>
+      <c r="F10" s="4" t="n"/>
+      <c r="G10" s="4" t="n"/>
       <c r="H10" s="4" t="n"/>
       <c r="I10" s="4" t="n"/>
       <c r="J10" s="4" t="n"/>
       <c r="K10" s="4" t="n"/>
       <c r="L10" s="4" t="n"/>
-      <c r="M10" s="12" t="inlineStr">
+      <c r="M10" s="4" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n"/>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>예시)  GRM188R71C104KA01D</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>Murata</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>MLCC</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>100nF ±10% / 16V / X7R</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>CAPC1608X90N</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="n"/>
+      <c r="I11" s="4" t="n"/>
+      <c r="J11" s="4" t="n"/>
+      <c r="K11" s="4" t="n"/>
+      <c r="L11" s="4" t="n"/>
+      <c r="M11" s="12" t="inlineStr">
         <is>
           <t>입력 형식 예시 행 (집계에서 제외됨). 실제 등록은 6행부터, 이 행은 지워도 됩니다. 검증상태 칸에는 미검증/빌드완료/검증완료 중 하나를 적습니다.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:M8"/>
+  <autoFilter ref="A5:M9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/footprints/parts_registry.xlsx
+++ b/footprints/parts_registry.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Legend" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'V2000'!$A$5:$M$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'V2000'!$A$5:$M$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -559,7 +559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P8"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -974,30 +974,86 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4" t="n"/>
-      <c r="B6" s="4" t="n"/>
-      <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="n"/>
-      <c r="E6" s="4" t="n"/>
-      <c r="F6" s="4" t="n"/>
-      <c r="G6" s="4" t="n"/>
-      <c r="H6" s="4" t="n"/>
-      <c r="I6" s="4" t="n"/>
-      <c r="J6" s="4" t="n"/>
-      <c r="K6" s="4" t="n"/>
-      <c r="L6" s="4" t="n"/>
-      <c r="M6" s="4" t="n"/>
-      <c r="N6" s="4" t="n"/>
-      <c r="O6" s="4" t="n"/>
-      <c r="P6" s="4" t="n"/>
+    <row r="6" ht="46" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>SOIC127P600X175-9M</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>S8E (SOIC-8 .150" 노출패드)</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>리드 1.57 x 0.76 / 노출패드 2.26 x 2.99</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>3.988 x 5.004 x 1.752max</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>x ±3.70 / y ±2.602</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>리드=벤더랜드 1.143 오프셋 / 노출패드=2x3 윈도우 70.0%</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>규칙2로 토 0.50 연장(벤더 1.143→1.57). 규칙4 이탈 — 페이스트는 벤더량 유지. 방향은 p.2 TOP VIEW 기준(p.26 기구도면과 90도 다름)</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>미검증</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>buildsoic127.il</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>LT8304 DS 8304fa p.2 Pin Config / p.26 Package Description</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>※ DRC / 검증상태는 axlDRCUpdate(t) 와 extracta 대조를 실제로 돌린 뒤에만 갱신할 것.</t>
-        </is>
-      </c>
+      <c r="A7" s="4" t="n"/>
       <c r="B7" s="4" t="n"/>
       <c r="C7" s="4" t="n"/>
       <c r="D7" s="4" t="n"/>
@@ -1017,7 +1073,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>※ 네 풋프린트 모두 이 세션에서는 빌드하지 못했습니다 (Allegro/extracta 부재). 스크립트만 작성된 상태입니다.</t>
+          <t>※ DRC / 검증상태는 axlDRCUpdate(t) 와 extracta 대조를 실제로 돌린 뒤에만 갱신할 것.</t>
         </is>
       </c>
       <c r="B8" s="4" t="n"/>
@@ -1036,6 +1092,28 @@
       <c r="O8" s="4" t="n"/>
       <c r="P8" s="4" t="n"/>
     </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>※ 다섯 풋프린트 모두 이 세션에서는 빌드하지 못했습니다 (Allegro/extracta 부재). 스크립트만 작성된 상태입니다.</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n"/>
+      <c r="C9" s="4" t="n"/>
+      <c r="D9" s="4" t="n"/>
+      <c r="E9" s="4" t="n"/>
+      <c r="F9" s="4" t="n"/>
+      <c r="G9" s="4" t="n"/>
+      <c r="H9" s="4" t="n"/>
+      <c r="I9" s="4" t="n"/>
+      <c r="J9" s="4" t="n"/>
+      <c r="K9" s="4" t="n"/>
+      <c r="L9" s="4" t="n"/>
+      <c r="M9" s="4" t="n"/>
+      <c r="N9" s="4" t="n"/>
+      <c r="O9" s="4" t="n"/>
+      <c r="P9" s="4" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -1048,7 +1126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1486,66 +1564,131 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="4" t="n"/>
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="4" t="n"/>
-      <c r="D10" s="4" t="n"/>
-      <c r="E10" s="4" t="n"/>
-      <c r="F10" s="4" t="n"/>
-      <c r="G10" s="4" t="n"/>
-      <c r="H10" s="4" t="n"/>
-      <c r="I10" s="4" t="n"/>
-      <c r="J10" s="4" t="n"/>
-      <c r="K10" s="4" t="n"/>
-      <c r="L10" s="4" t="n"/>
-      <c r="M10" s="4" t="n"/>
+    <row r="10" ht="42" customHeight="1">
+      <c r="A10" s="10">
+        <f>ROW()-5</f>
+        <v/>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>LT8304ES8E#PBF</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Analog Devices (Linear)</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>절연 플라이백 컨버터</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3~100Vin / 150V 2A DMOS / 24W / no-opto 절연 / θJA 33°C/W / Tj -40~+125°C</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>S8E (SOIC-8 노출패드)</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>SOIC127P600X175-9M</t>
+        </is>
+      </c>
+      <c r="H10" s="11">
+        <f>IFERROR(INDEX(Footprints!$D$2:$D$1000,MATCH($G10,Footprints!$A$2:$A$1000,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>LT8304/LT8304-1 DS 8304fa</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>buildsoic127.il</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>미검증</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>핀9=노출패드=GND, 반드시 납땜. 1 TC/2 RREF/3 RFB/4 SW/5 GND/6 VIN/7 INTVCC/8 EN·UVLO. LT8304-1 도 동일 패키지</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n"/>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>예시)  GRM188R71C104KA01D</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>Murata</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>MLCC</t>
-        </is>
-      </c>
-      <c r="E11" s="12" t="inlineStr">
-        <is>
-          <t>100nF ±10% / 16V / X7R</t>
-        </is>
-      </c>
-      <c r="F11" s="12" t="inlineStr">
-        <is>
-          <t>0603</t>
-        </is>
-      </c>
-      <c r="G11" s="12" t="inlineStr">
-        <is>
-          <t>CAPC1608X90N</t>
-        </is>
-      </c>
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="4" t="n"/>
+      <c r="E11" s="4" t="n"/>
+      <c r="F11" s="4" t="n"/>
+      <c r="G11" s="4" t="n"/>
       <c r="H11" s="4" t="n"/>
       <c r="I11" s="4" t="n"/>
       <c r="J11" s="4" t="n"/>
       <c r="K11" s="4" t="n"/>
       <c r="L11" s="4" t="n"/>
-      <c r="M11" s="12" t="inlineStr">
+      <c r="M11" s="4" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n"/>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>예시)  GRM188R71C104KA01D</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>Murata</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>MLCC</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>100nF ±10% / 16V / X7R</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>CAPC1608X90N</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="n"/>
+      <c r="I12" s="4" t="n"/>
+      <c r="J12" s="4" t="n"/>
+      <c r="K12" s="4" t="n"/>
+      <c r="L12" s="4" t="n"/>
+      <c r="M12" s="12" t="inlineStr">
         <is>
           <t>입력 형식 예시 행 (집계에서 제외됨). 실제 등록은 6행부터, 이 행은 지워도 됩니다. 검증상태 칸에는 미검증/빌드완료/검증완료 중 하나를 적습니다.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:M9"/>
+  <autoFilter ref="A5:M10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/footprints/parts_registry.xlsx
+++ b/footprints/parts_registry.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Legend" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'V2000'!$A$5:$M$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'V2000'!$A$5:$M$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -559,7 +559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1052,30 +1052,86 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="n"/>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="n"/>
-      <c r="F7" s="4" t="n"/>
-      <c r="G7" s="4" t="n"/>
-      <c r="H7" s="4" t="n"/>
-      <c r="I7" s="4" t="n"/>
-      <c r="J7" s="4" t="n"/>
-      <c r="K7" s="4" t="n"/>
-      <c r="L7" s="4" t="n"/>
-      <c r="M7" s="4" t="n"/>
-      <c r="N7" s="4" t="n"/>
-      <c r="O7" s="4" t="n"/>
-      <c r="P7" s="4" t="n"/>
+    <row r="7" ht="46" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>SOP65P490X104-9M</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>PG-TSSOP-8 (노출다이패드)</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>리드 1.45 x 0.40 / 노출패드 1.75 x 2.05</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3.1 x 3.1 x 1.04max</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>x ±3.10 / y ±1.65</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>리드=벤더 스텐실 1.3 오프셋 / 노출패드=2x2 창 79.9%</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>규칙2로 토 0.15 연장(벤더 1.3→1.45). 마스크는 규칙6에 따라 데이터시트값(동판+0.05/변) 우선 → 마스크 웹 0.15. 방향은 p.7 Top View 기준</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>미검증</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>buildsop65p490.il</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>Infineon 2EDN752x DS Rev2.7 p.7 Pin Config / p.27 outline / p.28 footprint</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>※ DRC / 검증상태는 axlDRCUpdate(t) 와 extracta 대조를 실제로 돌린 뒤에만 갱신할 것.</t>
-        </is>
-      </c>
+      <c r="A8" s="4" t="n"/>
       <c r="B8" s="4" t="n"/>
       <c r="C8" s="4" t="n"/>
       <c r="D8" s="4" t="n"/>
@@ -1095,7 +1151,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>※ 다섯 풋프린트 모두 이 세션에서는 빌드하지 못했습니다 (Allegro/extracta 부재). 스크립트만 작성된 상태입니다.</t>
+          <t>※ DRC / 검증상태는 axlDRCUpdate(t) 와 extracta 대조를 실제로 돌린 뒤에만 갱신할 것.</t>
         </is>
       </c>
       <c r="B9" s="4" t="n"/>
@@ -1114,6 +1170,28 @@
       <c r="O9" s="4" t="n"/>
       <c r="P9" s="4" t="n"/>
     </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>※ 여섯 풋프린트 모두 이 세션에서는 빌드하지 못했습니다 (Allegro/extracta 부재). 스크립트만 작성된 상태입니다.</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n"/>
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="4" t="n"/>
+      <c r="F10" s="4" t="n"/>
+      <c r="G10" s="4" t="n"/>
+      <c r="H10" s="4" t="n"/>
+      <c r="I10" s="4" t="n"/>
+      <c r="J10" s="4" t="n"/>
+      <c r="K10" s="4" t="n"/>
+      <c r="L10" s="4" t="n"/>
+      <c r="M10" s="4" t="n"/>
+      <c r="N10" s="4" t="n"/>
+      <c r="O10" s="4" t="n"/>
+      <c r="P10" s="4" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -1126,7 +1204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1629,66 +1707,131 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="4" t="n"/>
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="n"/>
-      <c r="E11" s="4" t="n"/>
-      <c r="F11" s="4" t="n"/>
-      <c r="G11" s="4" t="n"/>
-      <c r="H11" s="4" t="n"/>
-      <c r="I11" s="4" t="n"/>
-      <c r="J11" s="4" t="n"/>
-      <c r="K11" s="4" t="n"/>
-      <c r="L11" s="4" t="n"/>
-      <c r="M11" s="4" t="n"/>
+    <row r="11" ht="42" customHeight="1">
+      <c r="A11" s="10">
+        <f>ROW()-5</f>
+        <v/>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>2EDN7524RXTMA1</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Infineon</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>듀얼 게이트 드라이버</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2ch x 5A / 4.5~20V / UVLO 4.2V / 비반전 / 전파지연 17ns / RthJA 64 K/W</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>PG-TSSOP-8 (노출다이패드)</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>SOP65P490X104-9M</t>
+        </is>
+      </c>
+      <c r="H11" s="11">
+        <f>IFERROR(INDEX(Footprints!$D$2:$D$1000,MATCH($G11,Footprints!$A$2:$A$1000,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>2EDN752x/2EDN852x DS Rev 2.7 (2025-03-18)</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>buildsop65p490.il</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>미검증</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>핀9=노출다이패드, GND(핀3)에 연결 필수. 1 ENA/2 INA/3 GND/4 INB/5 OUTB/6 VDD/7 OUTA/8 ENB. 마스크 웹 0.15 — 팹 전역 마스크 확장 금지</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n"/>
-      <c r="B12" s="12" t="inlineStr">
-        <is>
-          <t>예시)  GRM188R71C104KA01D</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>Murata</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>MLCC</t>
-        </is>
-      </c>
-      <c r="E12" s="12" t="inlineStr">
-        <is>
-          <t>100nF ±10% / 16V / X7R</t>
-        </is>
-      </c>
-      <c r="F12" s="12" t="inlineStr">
-        <is>
-          <t>0603</t>
-        </is>
-      </c>
-      <c r="G12" s="12" t="inlineStr">
-        <is>
-          <t>CAPC1608X90N</t>
-        </is>
-      </c>
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="4" t="n"/>
+      <c r="E12" s="4" t="n"/>
+      <c r="F12" s="4" t="n"/>
+      <c r="G12" s="4" t="n"/>
       <c r="H12" s="4" t="n"/>
       <c r="I12" s="4" t="n"/>
       <c r="J12" s="4" t="n"/>
       <c r="K12" s="4" t="n"/>
       <c r="L12" s="4" t="n"/>
-      <c r="M12" s="12" t="inlineStr">
+      <c r="M12" s="4" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n"/>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>예시)  GRM188R71C104KA01D</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>Murata</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>MLCC</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>100nF ±10% / 16V / X7R</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>CAPC1608X90N</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="n"/>
+      <c r="I13" s="4" t="n"/>
+      <c r="J13" s="4" t="n"/>
+      <c r="K13" s="4" t="n"/>
+      <c r="L13" s="4" t="n"/>
+      <c r="M13" s="12" t="inlineStr">
         <is>
           <t>입력 형식 예시 행 (집계에서 제외됨). 실제 등록은 6행부터, 이 행은 지워도 됩니다. 검증상태 칸에는 미검증/빌드완료/검증완료 중 하나를 적습니다.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:M10"/>
+  <autoFilter ref="A5:M11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/footprints/parts_registry.xlsx
+++ b/footprints/parts_registry.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Legend" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'V2000'!$A$5:$M$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'V2000'!$A$5:$M$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -559,7 +559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1130,30 +1130,88 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="4" t="n"/>
-      <c r="B8" s="4" t="n"/>
-      <c r="C8" s="4" t="n"/>
-      <c r="D8" s="4" t="n"/>
-      <c r="E8" s="4" t="n"/>
-      <c r="F8" s="4" t="n"/>
-      <c r="G8" s="4" t="n"/>
-      <c r="H8" s="4" t="n"/>
-      <c r="I8" s="4" t="n"/>
-      <c r="J8" s="4" t="n"/>
-      <c r="K8" s="4" t="n"/>
-      <c r="L8" s="4" t="n"/>
-      <c r="M8" s="4" t="n"/>
-      <c r="N8" s="4" t="n"/>
-      <c r="O8" s="4" t="n"/>
-      <c r="P8" s="4" t="n"/>
+    <row r="8" ht="46" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>INDC1608X95M</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1608 메트릭 / 0603 인치 칩</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1.03 x 0.70</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1.75 x 0.95 x 0.95max</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>x ±1.48 / y ±0.70</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>벤더랜드 0.65 오프셋 (규칙4 칩 조항)</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>규칙2로 토 0.505 연장(벤더 0.65→1.03). 이탈 없음. 데이터시트 전면 'Reference Only' 워터마크</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>미검증</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>buildindc1608.il</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>Murata JENF243A_0003AM-01 p.5 외형 / p.10 12.1 Land dimensions</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>※ DRC / 검증상태는 axlDRCUpdate(t) 와 extracta 대조를 실제로 돌린 뒤에만 갱신할 것.</t>
-        </is>
-      </c>
+      <c r="A9" s="4" t="n"/>
       <c r="B9" s="4" t="n"/>
       <c r="C9" s="4" t="n"/>
       <c r="D9" s="4" t="n"/>
@@ -1173,7 +1231,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>※ 여섯 풋프린트 모두 이 세션에서는 빌드하지 못했습니다 (Allegro/extracta 부재). 스크립트만 작성된 상태입니다.</t>
+          <t>※ DRC / 검증상태는 axlDRCUpdate(t) 와 extracta 대조를 실제로 돌린 뒤에만 갱신할 것.</t>
         </is>
       </c>
       <c r="B10" s="4" t="n"/>
@@ -1192,6 +1250,28 @@
       <c r="O10" s="4" t="n"/>
       <c r="P10" s="4" t="n"/>
     </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>※ 일곱 풋프린트 모두 이 세션에서는 빌드하지 못했습니다 (Allegro/extracta 부재). 스크립트만 작성된 상태입니다.</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="4" t="n"/>
+      <c r="E11" s="4" t="n"/>
+      <c r="F11" s="4" t="n"/>
+      <c r="G11" s="4" t="n"/>
+      <c r="H11" s="4" t="n"/>
+      <c r="I11" s="4" t="n"/>
+      <c r="J11" s="4" t="n"/>
+      <c r="K11" s="4" t="n"/>
+      <c r="L11" s="4" t="n"/>
+      <c r="M11" s="4" t="n"/>
+      <c r="N11" s="4" t="n"/>
+      <c r="O11" s="4" t="n"/>
+      <c r="P11" s="4" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -1204,7 +1284,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1772,66 +1852,131 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="4" t="n"/>
-      <c r="B12" s="4" t="n"/>
-      <c r="C12" s="4" t="n"/>
-      <c r="D12" s="4" t="n"/>
-      <c r="E12" s="4" t="n"/>
-      <c r="F12" s="4" t="n"/>
-      <c r="G12" s="4" t="n"/>
-      <c r="H12" s="4" t="n"/>
-      <c r="I12" s="4" t="n"/>
-      <c r="J12" s="4" t="n"/>
-      <c r="K12" s="4" t="n"/>
-      <c r="L12" s="4" t="n"/>
-      <c r="M12" s="4" t="n"/>
+    <row r="12" ht="42" customHeight="1">
+      <c r="A12" s="10">
+        <f>ROW()-5</f>
+        <v/>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>BLM18SP300SN1D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Murata</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>칩 페라이트 비드</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>30±10Ω @100MHz / 정격 6000mA(85°C)·4000mA(125°C) / DCR 0.008Ω max / -55~+125°C / DC 전원라인용</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1608 메트릭 (0603)</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>INDC1608X95M</t>
+        </is>
+      </c>
+      <c r="H12" s="11">
+        <f>IFERROR(INDEX(Footprints!$D$2:$D$1000,MATCH($G12,Footprints!$A$2:$A$1000,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Murata JENF243A_0003AM-01 (Reference Only)</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>buildindc1608.il</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>미검증</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>무극성. 정격전류가 커서 연결 패턴 폭 d 요구: 35µm 동박에서 6.4mm (18µm·70µm은 규정 없음) — 레이아웃에서 확보할 것</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n"/>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>예시)  GRM188R71C104KA01D</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>Murata</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>MLCC</t>
-        </is>
-      </c>
-      <c r="E13" s="12" t="inlineStr">
-        <is>
-          <t>100nF ±10% / 16V / X7R</t>
-        </is>
-      </c>
-      <c r="F13" s="12" t="inlineStr">
-        <is>
-          <t>0603</t>
-        </is>
-      </c>
-      <c r="G13" s="12" t="inlineStr">
-        <is>
-          <t>CAPC1608X90N</t>
-        </is>
-      </c>
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="4" t="n"/>
+      <c r="E13" s="4" t="n"/>
+      <c r="F13" s="4" t="n"/>
+      <c r="G13" s="4" t="n"/>
       <c r="H13" s="4" t="n"/>
       <c r="I13" s="4" t="n"/>
       <c r="J13" s="4" t="n"/>
       <c r="K13" s="4" t="n"/>
       <c r="L13" s="4" t="n"/>
-      <c r="M13" s="12" t="inlineStr">
+      <c r="M13" s="4" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n"/>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>예시)  GRM188R71C104KA01D</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>Murata</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>MLCC</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>100nF ±10% / 16V / X7R</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>CAPC1608X90N</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="n"/>
+      <c r="I14" s="4" t="n"/>
+      <c r="J14" s="4" t="n"/>
+      <c r="K14" s="4" t="n"/>
+      <c r="L14" s="4" t="n"/>
+      <c r="M14" s="12" t="inlineStr">
         <is>
           <t>입력 형식 예시 행 (집계에서 제외됨). 실제 등록은 6행부터, 이 행은 지워도 됩니다. 검증상태 칸에는 미검증/빌드완료/검증완료 중 하나를 적습니다.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:M11"/>
+  <autoFilter ref="A5:M12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/footprints/parts_registry.xlsx
+++ b/footprints/parts_registry.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Legend" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'V2000'!$A$5:$M$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'V2000'!$A$5:$M$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -559,7 +559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:P12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1210,30 +1210,86 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="n"/>
-      <c r="B9" s="4" t="n"/>
-      <c r="C9" s="4" t="n"/>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="4" t="n"/>
-      <c r="F9" s="4" t="n"/>
-      <c r="G9" s="4" t="n"/>
-      <c r="H9" s="4" t="n"/>
-      <c r="I9" s="4" t="n"/>
-      <c r="J9" s="4" t="n"/>
-      <c r="K9" s="4" t="n"/>
-      <c r="L9" s="4" t="n"/>
-      <c r="M9" s="4" t="n"/>
-      <c r="N9" s="4" t="n"/>
-      <c r="O9" s="4" t="n"/>
-      <c r="P9" s="4" t="n"/>
+    <row r="9" ht="46" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>SOT95P280X145-5M</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>DBV0005A (SOT-23-5)</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1.25 x 0.60</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1.75 x 3.05 x 1.45max</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>x ±2.10 / y ±1.675</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>벤더 스텐실 1.1 오프셋</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>규칙2로 토 0.15 연장(벤더 1.1→1.25). 이탈 없음. 마스크는 규칙6에 따라 데이터시트값(NSMD, 동판+0.07/변) 우선 → 웹 0.21</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>미검증</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>buildsot95p280.il</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>TI SLVSE13J p.3 Pin Functions / p.59 Package Outline / p.60 Board Layout / p.61 Stencil</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>※ DRC / 검증상태는 axlDRCUpdate(t) 와 extracta 대조를 실제로 돌린 뒤에만 갱신할 것.</t>
-        </is>
-      </c>
+      <c r="A10" s="4" t="n"/>
       <c r="B10" s="4" t="n"/>
       <c r="C10" s="4" t="n"/>
       <c r="D10" s="4" t="n"/>
@@ -1253,7 +1309,7 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>※ 일곱 풋프린트 모두 이 세션에서는 빌드하지 못했습니다 (Allegro/extracta 부재). 스크립트만 작성된 상태입니다.</t>
+          <t>※ DRC / 검증상태는 axlDRCUpdate(t) 와 extracta 대조를 실제로 돌린 뒤에만 갱신할 것.</t>
         </is>
       </c>
       <c r="B11" s="4" t="n"/>
@@ -1272,6 +1328,28 @@
       <c r="O11" s="4" t="n"/>
       <c r="P11" s="4" t="n"/>
     </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>※ 여덟 풋프린트 모두 이 세션에서는 빌드하지 못했습니다 (Allegro/extracta 부재). 스크립트만 작성된 상태입니다.</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="4" t="n"/>
+      <c r="E12" s="4" t="n"/>
+      <c r="F12" s="4" t="n"/>
+      <c r="G12" s="4" t="n"/>
+      <c r="H12" s="4" t="n"/>
+      <c r="I12" s="4" t="n"/>
+      <c r="J12" s="4" t="n"/>
+      <c r="K12" s="4" t="n"/>
+      <c r="L12" s="4" t="n"/>
+      <c r="M12" s="4" t="n"/>
+      <c r="N12" s="4" t="n"/>
+      <c r="O12" s="4" t="n"/>
+      <c r="P12" s="4" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -1284,7 +1362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1917,66 +1995,131 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="n"/>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="4" t="n"/>
-      <c r="E13" s="4" t="n"/>
-      <c r="F13" s="4" t="n"/>
-      <c r="G13" s="4" t="n"/>
-      <c r="H13" s="4" t="n"/>
-      <c r="I13" s="4" t="n"/>
-      <c r="J13" s="4" t="n"/>
-      <c r="K13" s="4" t="n"/>
-      <c r="L13" s="4" t="n"/>
-      <c r="M13" s="4" t="n"/>
+    <row r="13" ht="42" customHeight="1">
+      <c r="A13" s="10">
+        <f>ROW()-5</f>
+        <v/>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>TLV7041DBVR</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Texas Instruments</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>나노파워 비교기 (싱글)</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1.6~6.5V / Iq 315nA / 오픈드레인 출력(704x) / 전파지연 3µs / 레일투레일 입력 / -40~+125°C</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>SOT-23-5 (DBV0005A)</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>SOT95P280X145-5M</t>
+        </is>
+      </c>
+      <c r="H13" s="11">
+        <f>IFERROR(INDEX(Footprints!$D$2:$D$1000,MATCH($G13,Footprints!$A$2:$A$1000,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>TI SLVSE13J (2024-11 rev)</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>buildsot95p280.il</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>미검증</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>1 OUT/2 V-/3 IN+/4 IN-/5 V+ (표준 'North West' 핀아웃). 같은 SOT-23-5 에 7041S·7041L 핀아웃 변형이 있으나 랜드는 동일 — 풋프린트는 1개, 구분은 심볼에서</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n"/>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>예시)  GRM188R71C104KA01D</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>Murata</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>MLCC</t>
-        </is>
-      </c>
-      <c r="E14" s="12" t="inlineStr">
-        <is>
-          <t>100nF ±10% / 16V / X7R</t>
-        </is>
-      </c>
-      <c r="F14" s="12" t="inlineStr">
-        <is>
-          <t>0603</t>
-        </is>
-      </c>
-      <c r="G14" s="12" t="inlineStr">
-        <is>
-          <t>CAPC1608X90N</t>
-        </is>
-      </c>
+      <c r="B14" s="4" t="n"/>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="n"/>
+      <c r="G14" s="4" t="n"/>
       <c r="H14" s="4" t="n"/>
       <c r="I14" s="4" t="n"/>
       <c r="J14" s="4" t="n"/>
       <c r="K14" s="4" t="n"/>
       <c r="L14" s="4" t="n"/>
-      <c r="M14" s="12" t="inlineStr">
+      <c r="M14" s="4" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n"/>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>예시)  GRM188R71C104KA01D</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>Murata</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>MLCC</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>100nF ±10% / 16V / X7R</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>CAPC1608X90N</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="n"/>
+      <c r="I15" s="4" t="n"/>
+      <c r="J15" s="4" t="n"/>
+      <c r="K15" s="4" t="n"/>
+      <c r="L15" s="4" t="n"/>
+      <c r="M15" s="12" t="inlineStr">
         <is>
           <t>입력 형식 예시 행 (집계에서 제외됨). 실제 등록은 6행부터, 이 행은 지워도 됩니다. 검증상태 칸에는 미검증/빌드완료/검증완료 중 하나를 적습니다.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:M12"/>
+  <autoFilter ref="A5:M13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/footprints/parts_registry.xlsx
+++ b/footprints/parts_registry.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Legend" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'V2000'!$A$5:$M$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'V2000'!$A$5:$M$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -559,7 +559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P12"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1288,30 +1288,86 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="4" t="n"/>
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="4" t="n"/>
-      <c r="D10" s="4" t="n"/>
-      <c r="E10" s="4" t="n"/>
-      <c r="F10" s="4" t="n"/>
-      <c r="G10" s="4" t="n"/>
-      <c r="H10" s="4" t="n"/>
-      <c r="I10" s="4" t="n"/>
-      <c r="J10" s="4" t="n"/>
-      <c r="K10" s="4" t="n"/>
-      <c r="L10" s="4" t="n"/>
-      <c r="M10" s="4" t="n"/>
-      <c r="N10" s="4" t="n"/>
-      <c r="O10" s="4" t="n"/>
-      <c r="P10" s="4" t="n"/>
+    <row r="10" ht="46" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>SOT95P237X112-3M</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>DBZ0003A (SOT-23-3)</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1.42 x 0.60</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1.4 x 3.04 x 1.12max</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>x ±1.92 / y ±1.67</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>벤더 스텐실 1.3 오프셋</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>규칙2로 토 0.12 연장(벤더 1.3→1.42). 이탈 없음. 마스크는 규칙6에 따라 데이터시트값(NSMD, 동판+0.07/변) 우선 → 웹 1.16</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>미검증</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>buildsot95p237.il</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>TI SBVS032K p.3 Pin Config / p.34 Package Outline / p.35 Board Layout / p.36 Stencil</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>※ DRC / 검증상태는 axlDRCUpdate(t) 와 extracta 대조를 실제로 돌린 뒤에만 갱신할 것.</t>
-        </is>
-      </c>
+      <c r="A11" s="4" t="n"/>
       <c r="B11" s="4" t="n"/>
       <c r="C11" s="4" t="n"/>
       <c r="D11" s="4" t="n"/>
@@ -1331,7 +1387,7 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>※ 여덟 풋프린트 모두 이 세션에서는 빌드하지 못했습니다 (Allegro/extracta 부재). 스크립트만 작성된 상태입니다.</t>
+          <t>※ DRC / 검증상태는 axlDRCUpdate(t) 와 extracta 대조를 실제로 돌린 뒤에만 갱신할 것.</t>
         </is>
       </c>
       <c r="B12" s="4" t="n"/>
@@ -1350,6 +1406,28 @@
       <c r="O12" s="4" t="n"/>
       <c r="P12" s="4" t="n"/>
     </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>※ 아홉 풋프린트 모두 이 세션에서는 빌드하지 못했습니다 (Allegro/extracta 부재). 스크립트만 작성된 상태입니다.</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="4" t="n"/>
+      <c r="E13" s="4" t="n"/>
+      <c r="F13" s="4" t="n"/>
+      <c r="G13" s="4" t="n"/>
+      <c r="H13" s="4" t="n"/>
+      <c r="I13" s="4" t="n"/>
+      <c r="J13" s="4" t="n"/>
+      <c r="K13" s="4" t="n"/>
+      <c r="L13" s="4" t="n"/>
+      <c r="M13" s="4" t="n"/>
+      <c r="N13" s="4" t="n"/>
+      <c r="O13" s="4" t="n"/>
+      <c r="P13" s="4" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -1362,7 +1440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2060,66 +2138,131 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="n"/>
-      <c r="B14" s="4" t="n"/>
-      <c r="C14" s="4" t="n"/>
-      <c r="D14" s="4" t="n"/>
-      <c r="E14" s="4" t="n"/>
-      <c r="F14" s="4" t="n"/>
-      <c r="G14" s="4" t="n"/>
-      <c r="H14" s="4" t="n"/>
-      <c r="I14" s="4" t="n"/>
-      <c r="J14" s="4" t="n"/>
-      <c r="K14" s="4" t="n"/>
-      <c r="L14" s="4" t="n"/>
-      <c r="M14" s="4" t="n"/>
+    <row r="14" ht="42" customHeight="1">
+      <c r="A14" s="10">
+        <f>ROW()-5</f>
+        <v/>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>REF3030AIDBZR</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Texas Instruments</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>전압 레퍼런스 (직렬)</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Vout 3.0V / 초기정확도 ±0.2% / 드리프트 75ppm/°C / Iq 42µA typ / Iout 25mA / -40~+125°C / 마킹 R30F</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>SOT-23-3 (DBZ0003A)</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>SOT95P237X112-3M</t>
+        </is>
+      </c>
+      <c r="H14" s="11">
+        <f>IFERROR(INDEX(Footprints!$D$2:$D$1000,MATCH($G14,Footprints!$A$2:$A$1000,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>TI SBVS032K (2025-12 rev)</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>buildsot95p237.il</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>미검증</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>1 IN / 2 OUT / 3 GND. 같은 DBZ 패키지의 REF30E 계열(REF3030EAIDBZR 등)도 랜드 동일 — 풋프린트 1개 공용</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n"/>
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t>예시)  GRM188R71C104KA01D</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>Murata</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>MLCC</t>
-        </is>
-      </c>
-      <c r="E15" s="12" t="inlineStr">
-        <is>
-          <t>100nF ±10% / 16V / X7R</t>
-        </is>
-      </c>
-      <c r="F15" s="12" t="inlineStr">
-        <is>
-          <t>0603</t>
-        </is>
-      </c>
-      <c r="G15" s="12" t="inlineStr">
-        <is>
-          <t>CAPC1608X90N</t>
-        </is>
-      </c>
+      <c r="B15" s="4" t="n"/>
+      <c r="C15" s="4" t="n"/>
+      <c r="D15" s="4" t="n"/>
+      <c r="E15" s="4" t="n"/>
+      <c r="F15" s="4" t="n"/>
+      <c r="G15" s="4" t="n"/>
       <c r="H15" s="4" t="n"/>
       <c r="I15" s="4" t="n"/>
       <c r="J15" s="4" t="n"/>
       <c r="K15" s="4" t="n"/>
       <c r="L15" s="4" t="n"/>
-      <c r="M15" s="12" t="inlineStr">
+      <c r="M15" s="4" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n"/>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>예시)  GRM188R71C104KA01D</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>Murata</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>MLCC</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>100nF ±10% / 16V / X7R</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>CAPC1608X90N</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="n"/>
+      <c r="I16" s="4" t="n"/>
+      <c r="J16" s="4" t="n"/>
+      <c r="K16" s="4" t="n"/>
+      <c r="L16" s="4" t="n"/>
+      <c r="M16" s="12" t="inlineStr">
         <is>
           <t>입력 형식 예시 행 (집계에서 제외됨). 실제 등록은 6행부터, 이 행은 지워도 됩니다. 검증상태 칸에는 미검증/빌드완료/검증완료 중 하나를 적습니다.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:M13"/>
+  <autoFilter ref="A5:M14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
